--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461298.2972870751</v>
+        <v>461298</v>
       </c>
       <c r="R2" t="n">
-        <v>6494240.823389799</v>
+        <v>6494241</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1995-07-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461298.2972870751</v>
+        <v>461298</v>
       </c>
       <c r="R3" t="n">
-        <v>6494240.823389799</v>
+        <v>6494241</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +844,9 @@
           <t>1995-07-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1995-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461298.2972870751</v>
+        <v>461298</v>
       </c>
       <c r="R4" t="n">
-        <v>6494240.823389799</v>
+        <v>6494241</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -980,19 +945,9 @@
           <t>1995-07-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1995-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97451</v>
+        <v>97457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98608</v>
+        <v>98616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98616</v>
+        <v>98622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242526</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2957952</v>
       </c>
       <c r="B3" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>4211677</v>
       </c>
       <c r="B4" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10833-2025 artfynd.xlsx
+++ b/artfynd/A 10833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4242526</v>
+        <v>2957952</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2957952</v>
+        <v>4211677</v>
       </c>
       <c r="B3" t="n">
-        <v>98683</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4211677</v>
+        <v>4242526</v>
       </c>
       <c r="B4" t="n">
-        <v>97517</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -971,6 +971,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4416517</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogsväg, brant 1,3 km SO om ARVIDSTORP, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>461298</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6494241</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Töreboda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Beateberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1995-07-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1995-07-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Arne Thorsell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Västergötlands flora 2002</t>
         </is>
